--- a/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
@@ -3349,13 +3349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E273D715-015A-4CA0-97D1-217D4FE34E90}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17EB6F85-18E3-42A2-8D51-FA2949EE1E7C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A63641C-9BCC-4901-94DC-452B38B8BAC9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43CF1575-28B3-4319-B385-00ADA19156B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB64827A-05F8-49C5-8E82-57BDFB26F0CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370EE35F-9C0E-4699-9A15-695CAFC3155C}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
@@ -3349,13 +3349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17EB6F85-18E3-42A2-8D51-FA2949EE1E7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43995ADB-9A33-4942-A6FE-3F1AB85AC285}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43CF1575-28B3-4319-B385-00ADA19156B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE38ADCA-C6D4-43A1-8511-89A54407AB37}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{370EE35F-9C0E-4699-9A15-695CAFC3155C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363862C3-9918-4AA0-9538-CF5DD2CCC0F1}"/>
 </file>
--- a/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
+++ b/ksoft_old/docs/records/Item_Family_Stock_Records.xlsx
@@ -3349,13 +3349,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43995ADB-9A33-4942-A6FE-3F1AB85AC285}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E273D715-015A-4CA0-97D1-217D4FE34E90}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE38ADCA-C6D4-43A1-8511-89A54407AB37}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A63641C-9BCC-4901-94DC-452B38B8BAC9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363862C3-9918-4AA0-9538-CF5DD2CCC0F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB64827A-05F8-49C5-8E82-57BDFB26F0CA}"/>
 </file>